--- a/Economic modelling/Critical_sectors.xlsx
+++ b/Economic modelling/Critical_sectors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Abbreviation</t>
   </si>
@@ -25,33 +25,21 @@
     <t>ACCO</t>
   </si>
   <si>
-    <t>AETA</t>
-  </si>
-  <si>
     <t>AGRI</t>
   </si>
   <si>
     <t>CARE</t>
   </si>
   <si>
-    <t>CHEM</t>
-  </si>
-  <si>
     <t>CONS</t>
   </si>
   <si>
-    <t>EDUC</t>
-  </si>
-  <si>
     <t>ENGY</t>
   </si>
   <si>
     <t>FOOD</t>
   </si>
   <si>
-    <t>FORE</t>
-  </si>
-  <si>
     <t>HLTH</t>
   </si>
   <si>
@@ -61,72 +49,33 @@
     <t>LAMC</t>
   </si>
   <si>
-    <t>LTPP</t>
-  </si>
-  <si>
-    <t>METL</t>
-  </si>
-  <si>
     <t>PADM</t>
   </si>
   <si>
-    <t>PAPR</t>
-  </si>
-  <si>
     <t>REAL</t>
   </si>
   <si>
-    <t>RETL</t>
-  </si>
-  <si>
-    <t>SISA</t>
-  </si>
-  <si>
-    <t>SPOR</t>
-  </si>
-  <si>
-    <t>WAST</t>
-  </si>
-  <si>
-    <t>WHOL</t>
-  </si>
-  <si>
-    <t>WOOD</t>
-  </si>
-  <si>
     <t>WSUP</t>
   </si>
   <si>
     <t>Accommodation and food service activities</t>
   </si>
   <si>
-    <t>Architectural and engineering activities; technical testing and analysis</t>
-  </si>
-  <si>
     <t>Crop and animal production, hunting and related service activities</t>
   </si>
   <si>
     <t>Residential care activities and social work activities without accommodation</t>
   </si>
   <si>
-    <t>Manufacture of chemicals and chemical products</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>Electricity, gas, steam and air conditioning supply</t>
   </si>
   <si>
     <t>Manufacture of food products; beverages and tobacco products</t>
   </si>
   <si>
-    <t>Forestry and logging</t>
-  </si>
-  <si>
     <t>Human health activities</t>
   </si>
   <si>
@@ -136,37 +85,10 @@
     <t>Legal and accounting activities; activities of head offices; management consultancy activities</t>
   </si>
   <si>
-    <t>Land transport and transport via pipelines</t>
-  </si>
-  <si>
-    <t>Manufacture of basic metals</t>
-  </si>
-  <si>
     <t>Public administration and defence; compulsory social security</t>
   </si>
   <si>
-    <t>Manufacture of paper and paper products</t>
-  </si>
-  <si>
     <t>Real estate activities</t>
-  </si>
-  <si>
-    <t>Retail trade, except of motor vehicles and motorcycles</t>
-  </si>
-  <si>
-    <t>Security and investigation, service and landscape, office administrative and support activities</t>
-  </si>
-  <si>
-    <t>Sports activities and amusement and recreation activities</t>
-  </si>
-  <si>
-    <t>Warehousing and support activities for transportation</t>
-  </si>
-  <si>
-    <t>Wholesale trade, except of motor vehicles and motorcycles</t>
-  </si>
-  <si>
-    <t>Manufacture of wood and of products of wood and cork, except furniture; manufacture of articles of straw and plaiting materials</t>
   </si>
   <si>
     <t>Water collection, treatment and supply</t>
@@ -527,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -543,7 +465,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -551,7 +473,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -559,7 +481,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -567,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -575,7 +497,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +505,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +513,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +529,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +537,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +545,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,111 +553,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
         <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Economic modelling/Critical_sectors.xlsx
+++ b/Economic modelling/Critical_sectors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Abbreviation</t>
   </si>
@@ -25,6 +25,9 @@
     <t>ACCO</t>
   </si>
   <si>
+    <t>AETA</t>
+  </si>
+  <si>
     <t>AGRI</t>
   </si>
   <si>
@@ -34,6 +37,9 @@
     <t>CONS</t>
   </si>
   <si>
+    <t>EDUC</t>
+  </si>
+  <si>
     <t>ENGY</t>
   </si>
   <si>
@@ -55,12 +61,18 @@
     <t>REAL</t>
   </si>
   <si>
+    <t>WHOL</t>
+  </si>
+  <si>
     <t>WSUP</t>
   </si>
   <si>
     <t>Accommodation and food service activities</t>
   </si>
   <si>
+    <t>Architectural and engineering activities; technical testing and analysis</t>
+  </si>
+  <si>
     <t>Crop and animal production, hunting and related service activities</t>
   </si>
   <si>
@@ -70,6 +82,9 @@
     <t>Construction</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>Electricity, gas, steam and air conditioning supply</t>
   </si>
   <si>
@@ -89,6 +104,9 @@
   </si>
   <si>
     <t>Real estate activities</t>
+  </si>
+  <si>
+    <t>Wholesale trade, except of motor vehicles and motorcycles</t>
   </si>
   <si>
     <t>Water collection, treatment and supply</t>
@@ -449,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -465,7 +483,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -473,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -481,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -489,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -497,7 +515,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -505,7 +523,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -513,7 +531,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -521,7 +539,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -529,7 +547,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -537,7 +555,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -545,7 +563,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -553,7 +571,31 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
